--- a/data/raw_data/Complementarity_independence_pressure_keywords.xlsx
+++ b/data/raw_data/Complementarity_independence_pressure_keywords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/Fortune500_SDG_Analysis/data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC9EA19-2CAF-F647-885E-85541005971F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3DD5E8-3732-454E-8D88-8DB93133238A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-39820" yWindow="1380" windowWidth="21080" windowHeight="22240" xr2:uid="{B271409B-AA80-5346-A4EF-8C6B0C389E3F}"/>
+    <workbookView minimized="1" xWindow="980" yWindow="760" windowWidth="29260" windowHeight="18880" xr2:uid="{B271409B-AA80-5346-A4EF-8C6B0C389E3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5469,7 +5469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5543,38 +5543,25 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -14043,27 +14030,27 @@
       <c r="A810" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D785:D1048576 D772 D739:D740 D731:D733 D743:D751 D720:D728 D673:D704 D709:D710 D667:D668 D1:D218 D220:D662">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B465:B1048576 B463 B461 B459 B457 B455 B1:B327 B330:B453">
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B465:B1048576 B463 B461 B459 B457 B455 B330:B453 B1:B327">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B465:B1048576 B463 B461 B459 B457 B455 B1:B327 B330:B453">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+  <conditionalFormatting sqref="C1:C390 C402:C1048576 C399 C392:C397">
+    <cfRule type="duplicateValues" dxfId="7" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C390 C402:C1048576 C399 C392:C397">
-    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="D785:D1048576 D772 D739:D740 D731:D733 D743:D751 D720:D728 D673:D704 D709:D710 D667:D668 D1:D218 D220:D662">
+    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14084,16 +14071,13 @@
   <dimension ref="A1:G475"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="41"/>
     <col min="2" max="2" width="40.83203125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="41" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="41"/>
-    <col min="5" max="5" width="17.83203125" style="41" customWidth="1"/>
-    <col min="6" max="6" width="77.5" style="41" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="41"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="77.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -14102,3236 +14086,2331 @@
       </c>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="E2" s="41" t="s">
+      <c r="C2" s="41"/>
+      <c r="E2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="43"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C3" s="42"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="47" t="s">
         <v>1616</v>
       </c>
-      <c r="E4"/>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="12" t="s">
         <v>852</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="E6"/>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="B7" s="44" t="s">
         <v>866</v>
       </c>
-      <c r="E7"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="B8" s="44" t="s">
         <v>867</v>
       </c>
-      <c r="E8"/>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="E9"/>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E10"/>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E11"/>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E12"/>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E13"/>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E14"/>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15"/>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E16"/>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B17" s="45" t="s">
+    </row>
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B17" s="44" t="s">
         <v>868</v>
       </c>
-      <c r="E17"/>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="s">
+    </row>
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B18" s="44" t="s">
         <v>869</v>
       </c>
-      <c r="E18"/>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B19" s="45" t="s">
+    </row>
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B19" s="44" t="s">
         <v>870</v>
       </c>
-      <c r="E19"/>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
+    </row>
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B20" s="44" t="s">
         <v>871</v>
       </c>
-      <c r="E20"/>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B21" s="45" t="s">
+    </row>
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B21" s="44" t="s">
         <v>872</v>
       </c>
-      <c r="E21"/>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B22" s="45" t="s">
+    </row>
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B22" s="44" t="s">
         <v>873</v>
       </c>
-      <c r="E22"/>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
+    </row>
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B23" s="44" t="s">
         <v>874</v>
       </c>
-      <c r="E23"/>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="s">
+    </row>
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B24" s="44" t="s">
         <v>875</v>
       </c>
-      <c r="E24"/>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B25" s="45" t="s">
+    </row>
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B25" s="44" t="s">
         <v>876</v>
       </c>
-      <c r="E25"/>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
+    </row>
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B26" s="44" t="s">
         <v>877</v>
       </c>
-      <c r="E26"/>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B27" s="45" t="s">
+    </row>
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B27" s="44" t="s">
         <v>878</v>
       </c>
-      <c r="E27"/>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E28"/>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B29" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E29"/>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="E30"/>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="E31"/>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E32"/>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E33"/>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E34"/>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E35"/>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="E36"/>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="E37"/>
-      <c r="F37"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="E38"/>
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="E39"/>
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="E40"/>
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="E41"/>
-      <c r="F41"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="E42"/>
-      <c r="F42"/>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B43" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E43"/>
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B44" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="E44"/>
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B45" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E45"/>
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B46" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E46"/>
-      <c r="F46"/>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B47" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="E47"/>
-      <c r="F47"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B48" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="E48"/>
-      <c r="F48"/>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E49"/>
-      <c r="F49"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="E50"/>
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="46" t="s">
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="E51"/>
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B52" s="46" t="s">
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="E52"/>
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B53" s="46" t="s">
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="E53"/>
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B54" s="46" t="s">
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="45" t="s">
         <v>289</v>
       </c>
-      <c r="E54"/>
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B55" s="46" t="s">
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="E55"/>
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B56" s="46" t="s">
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="E56"/>
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="46" t="s">
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="E57"/>
-      <c r="F57"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B58" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="E58"/>
-      <c r="F58"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B59" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E59"/>
-      <c r="F59"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B60" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="E60"/>
-      <c r="F60"/>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B61" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="E61"/>
-      <c r="F61"/>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B62" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="E62"/>
-      <c r="F62"/>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B63" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="E63"/>
-      <c r="F63"/>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B64" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="E64"/>
-      <c r="F64"/>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E65"/>
-      <c r="F65"/>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E66"/>
-      <c r="F66"/>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E67"/>
-      <c r="F67"/>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E68"/>
-      <c r="F68"/>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B69" s="48" t="s">
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B69" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E69"/>
-      <c r="F69"/>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B70" s="48" t="s">
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B70" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E70"/>
-      <c r="F70"/>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B71" s="48" t="s">
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B71" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E71"/>
-      <c r="F71"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B72" s="48" t="s">
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E72"/>
-      <c r="F72"/>
-    </row>
-    <row r="73" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B73" s="48" t="s">
+    </row>
+    <row r="73" spans="2:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="B73" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="51"/>
-      <c r="F73"/>
-    </row>
-    <row r="74" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B74" s="48" t="s">
+      <c r="E73" s="48"/>
+    </row>
+    <row r="74" spans="2:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="B74" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E74" s="51"/>
-      <c r="F74"/>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B75" s="48" t="s">
+      <c r="E74" s="48"/>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E75"/>
-      <c r="F75"/>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B76" s="48" t="s">
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B76" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E76"/>
-      <c r="F76"/>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="48" t="s">
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B77" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E77"/>
-      <c r="F77"/>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="41" t="s">
+      <c r="C78" t="s">
         <v>1614</v>
       </c>
-      <c r="E78"/>
-      <c r="F78"/>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E79"/>
-      <c r="F79"/>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E80"/>
-      <c r="F80"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B81" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E81"/>
-      <c r="F81"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B82" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="E82"/>
-      <c r="F82"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B83" s="14" t="s">
         <v>850</v>
       </c>
-      <c r="E83"/>
-      <c r="F83"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B84" s="14" t="s">
         <v>851</v>
       </c>
-      <c r="E84"/>
-      <c r="F84"/>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B85" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="E85"/>
-      <c r="F85"/>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B86" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E86"/>
-      <c r="F86"/>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B87" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E87"/>
-      <c r="F87"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B88" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E88"/>
-      <c r="F88"/>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B89" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E89"/>
-      <c r="F89"/>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B90" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E90"/>
-      <c r="F90"/>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B91" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E91"/>
-      <c r="F91"/>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B92" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92" s="50"/>
+      <c r="G92" s="47"/>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B93" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C93" s="44"/>
-      <c r="E93"/>
-      <c r="F93"/>
+      <c r="C93" s="43"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B94" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E94"/>
-      <c r="F94"/>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B95" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E95"/>
-      <c r="F95"/>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B96" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E96"/>
-      <c r="F96"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B97" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E97"/>
-      <c r="F97"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B98" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="E98"/>
-      <c r="F98"/>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B99" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E99"/>
-      <c r="F99"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B100" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="E100"/>
-      <c r="F100"/>
-    </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B101" s="13"/>
-      <c r="E101"/>
-      <c r="F101"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B102" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="E102"/>
-      <c r="F102"/>
-    </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B103" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E103"/>
-      <c r="F103"/>
-    </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B104" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E104"/>
-      <c r="F104"/>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B105" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="E105"/>
-      <c r="F105"/>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B106" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E106"/>
-      <c r="F106"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B107" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E107"/>
-      <c r="F107"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B108" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="E108"/>
-      <c r="F108"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B109" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E109"/>
-      <c r="F109"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B110" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="E110"/>
-      <c r="F110"/>
-    </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B111" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="E111"/>
-      <c r="F111"/>
-    </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B112" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="E112"/>
-      <c r="F112"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B113" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E113"/>
-      <c r="F113"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B114" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="E114"/>
-      <c r="F114"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B115" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E115"/>
-      <c r="F115"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B116" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E116"/>
-      <c r="F116"/>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B117" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E117"/>
-      <c r="F117"/>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B118" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E118"/>
-      <c r="F118"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B119" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E119"/>
-      <c r="F119"/>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B120" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E120"/>
-      <c r="F120"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B121" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E121"/>
-      <c r="F121"/>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B122" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="E122"/>
-      <c r="F122"/>
-    </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B123" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E123"/>
-      <c r="F123"/>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B124" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E124"/>
-      <c r="F124"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B125" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E125"/>
-      <c r="F125"/>
-    </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B126" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="E126"/>
-      <c r="F126"/>
-    </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B127" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E127"/>
-      <c r="F127"/>
-    </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B128" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E128"/>
-      <c r="F128"/>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B129" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E129"/>
-      <c r="F129"/>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B130" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E130"/>
-      <c r="F130"/>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B131" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E131"/>
-      <c r="F131"/>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B132" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="E132"/>
-      <c r="F132"/>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B133" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="E133"/>
-      <c r="F133"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B134" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E134"/>
-      <c r="F134"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B135" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="E135"/>
-      <c r="F135"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B136" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="E136"/>
-      <c r="F136"/>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B137" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E137"/>
-      <c r="F137"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B138" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="E138"/>
-      <c r="F138"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B139" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="E139"/>
-      <c r="F139"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B140" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="E140"/>
-      <c r="F140"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B141" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="E141"/>
-      <c r="F141"/>
-    </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B142" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="E142"/>
-      <c r="F142"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B143" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="E143"/>
-      <c r="F143"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B144" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="E144"/>
-      <c r="F144"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B145" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E145"/>
-      <c r="F145"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B146" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="E146"/>
-      <c r="F146"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B147" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="E147"/>
-      <c r="F147"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B148" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E148"/>
-      <c r="F148"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B149" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="E149"/>
-      <c r="F149"/>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B150" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="E150"/>
-      <c r="F150"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B151" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="E151"/>
-      <c r="F151"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B152" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E152"/>
-      <c r="F152"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B153" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="E153"/>
-      <c r="F153"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B154" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E154"/>
-      <c r="F154"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B155" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="E155"/>
-      <c r="F155"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B156" s="17" t="s">
         <v>1615</v>
       </c>
-      <c r="E156"/>
-      <c r="F156"/>
-    </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B157" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C157" s="50" t="s">
+      <c r="C157" s="47" t="s">
         <v>1617</v>
       </c>
-      <c r="E157"/>
-      <c r="F157"/>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B158" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E158"/>
-      <c r="F158"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B159" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E159"/>
-      <c r="F159"/>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B160" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E160"/>
-      <c r="F160"/>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B161" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E161"/>
-      <c r="F161"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B162" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="E162"/>
-      <c r="F162"/>
-    </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B163" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="E163"/>
-      <c r="F163"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B164" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="E164"/>
-      <c r="F164"/>
-    </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B165" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="E165"/>
-      <c r="F165"/>
-    </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B166" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E166"/>
-      <c r="F166"/>
-    </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B167" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="E167"/>
-      <c r="F167"/>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B168" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="E168"/>
-      <c r="F168"/>
-    </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B169" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E169"/>
-      <c r="F169"/>
-    </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B170" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E170"/>
-      <c r="F170"/>
-    </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B171" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E171"/>
-      <c r="F171"/>
-    </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B172" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="E172"/>
-      <c r="F172"/>
-    </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B173" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="E173"/>
-      <c r="F173"/>
-    </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B174" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E174"/>
-      <c r="F174"/>
-    </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B175" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="E175"/>
-      <c r="F175"/>
-    </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B176" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E176"/>
-      <c r="F176"/>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B177" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E177"/>
-      <c r="F177"/>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B178" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E178"/>
-      <c r="F178"/>
-    </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B179" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E179"/>
-      <c r="F179"/>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B180" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E180"/>
-      <c r="F180"/>
-    </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B181" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E181"/>
-      <c r="F181"/>
-    </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B182" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E182"/>
-      <c r="F182"/>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B183" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E183"/>
-      <c r="F183"/>
-    </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B184" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E184"/>
-      <c r="F184"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B185" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E185"/>
-      <c r="F185"/>
-    </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B186" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E186"/>
-      <c r="F186"/>
-    </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B187" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E187"/>
-      <c r="F187"/>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B188" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E188"/>
-      <c r="F188"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B189" s="41" t="s">
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" t="s">
         <v>266</v>
       </c>
-      <c r="E189"/>
-      <c r="F189"/>
-    </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B190" s="41" t="s">
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" t="s">
         <v>20</v>
       </c>
-      <c r="E190"/>
-      <c r="F190"/>
-    </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B191" s="41" t="s">
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" t="s">
         <v>1628</v>
       </c>
-      <c r="E191"/>
-      <c r="F191"/>
-    </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B192" s="41" t="s">
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192" t="s">
         <v>1629</v>
       </c>
-      <c r="E192"/>
-      <c r="F192"/>
-    </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B193" s="41" t="s">
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B193" t="s">
         <v>1632</v>
       </c>
-      <c r="C193" s="41" t="s">
+      <c r="C193" t="s">
         <v>1631</v>
       </c>
-      <c r="E193"/>
-      <c r="F193"/>
-    </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B194" s="41" t="s">
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B194" t="s">
         <v>1633</v>
       </c>
-      <c r="E194"/>
-      <c r="F194"/>
-    </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B195" s="41" t="s">
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B195" t="s">
         <v>1634</v>
       </c>
-      <c r="E195"/>
-      <c r="F195"/>
-    </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B196" s="41" t="s">
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B196" t="s">
         <v>1635</v>
       </c>
-      <c r="E196"/>
-      <c r="F196"/>
-    </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B197" s="41" t="s">
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B197" t="s">
         <v>1636</v>
       </c>
-      <c r="E197"/>
-      <c r="F197"/>
-    </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B198" s="41" t="s">
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
         <v>1637</v>
       </c>
-      <c r="E198"/>
-      <c r="F198"/>
-    </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B199" s="41" t="s">
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
         <v>1638</v>
       </c>
-      <c r="E199"/>
-      <c r="F199"/>
-    </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B200" s="41" t="s">
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
         <v>1639</v>
       </c>
-      <c r="E200"/>
-      <c r="F200"/>
-    </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B201" s="41" t="s">
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
         <v>1640</v>
       </c>
-      <c r="E201"/>
-      <c r="F201"/>
-    </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B202" s="41" t="s">
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
         <v>1641</v>
       </c>
-      <c r="E202"/>
-      <c r="F202"/>
-    </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B203" s="41" t="s">
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
         <v>1642</v>
       </c>
-      <c r="E203"/>
-      <c r="F203"/>
-    </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B204" s="41" t="s">
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B204" t="s">
         <v>1643</v>
       </c>
-      <c r="E204"/>
-      <c r="F204"/>
-    </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B205" s="41" t="s">
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B205" t="s">
         <v>1644</v>
       </c>
-      <c r="E205"/>
-      <c r="F205"/>
-    </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B206" s="41" t="s">
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B206" t="s">
         <v>1645</v>
       </c>
-      <c r="E206"/>
-      <c r="F206"/>
-    </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B207" s="41" t="s">
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B207" t="s">
         <v>1646</v>
       </c>
-      <c r="E207"/>
-      <c r="F207"/>
-    </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B208" s="41" t="s">
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B208" t="s">
         <v>1647</v>
       </c>
-      <c r="E208"/>
-      <c r="F208"/>
-    </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B209" s="41" t="s">
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B209" t="s">
         <v>1648</v>
       </c>
-      <c r="E209"/>
-      <c r="F209"/>
-    </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B210" s="41" t="s">
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B210" t="s">
         <v>1649</v>
       </c>
-      <c r="E210"/>
-      <c r="F210"/>
-    </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B211" s="41" t="s">
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B211" t="s">
         <v>1650</v>
       </c>
-      <c r="E211"/>
-      <c r="F211"/>
-    </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B212" s="41" t="s">
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B212" t="s">
         <v>1651</v>
       </c>
-      <c r="E212"/>
-      <c r="F212"/>
-    </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B213" s="41" t="s">
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B213" t="s">
         <v>1652</v>
       </c>
-      <c r="D213" s="49"/>
-      <c r="E213"/>
-      <c r="F213"/>
-    </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B214" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C214" s="50" t="s">
+      <c r="C214" s="47" t="s">
         <v>1620</v>
       </c>
-      <c r="E214"/>
-      <c r="F214"/>
-    </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B215" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E215"/>
-      <c r="F215"/>
-    </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B216" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E216"/>
-      <c r="F216"/>
-    </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B217" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E217"/>
-      <c r="F217"/>
-    </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B218" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="E218"/>
-      <c r="F218"/>
-    </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B219" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E219"/>
-      <c r="F219"/>
-    </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B220" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E220"/>
-      <c r="F220"/>
-    </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B221" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="E221"/>
-      <c r="F221"/>
-    </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B222" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="E222"/>
-      <c r="F222"/>
-    </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B223" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="E223"/>
-      <c r="F223"/>
-    </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B224" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="E224"/>
-      <c r="F224"/>
-    </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B225" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="E225"/>
-      <c r="F225"/>
-    </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B226" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="E226"/>
-      <c r="F226"/>
-    </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B227" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="E227"/>
-      <c r="F227"/>
-    </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B228" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="E228"/>
-      <c r="F228"/>
-    </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B229" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="E229"/>
-      <c r="F229"/>
-    </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B230" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E230"/>
-      <c r="F230"/>
-    </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B231" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E231"/>
-      <c r="F231"/>
-    </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B232" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E232"/>
-      <c r="F232"/>
-    </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B233" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="E233"/>
-      <c r="F233"/>
-    </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B234" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E234"/>
-      <c r="F234"/>
-    </row>
-    <row r="235" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B235" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="E235"/>
-      <c r="F235"/>
-    </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B236" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="E236"/>
-      <c r="F236"/>
-    </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B237" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E237"/>
-      <c r="F237"/>
-    </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B238" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E238"/>
-      <c r="F238"/>
-    </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B239" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="E239"/>
-      <c r="F239"/>
-    </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B240" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E240"/>
-      <c r="F240"/>
-    </row>
-    <row r="241" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B241" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E241"/>
-      <c r="F241"/>
-    </row>
-    <row r="242" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B242" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="E242"/>
-      <c r="F242"/>
-    </row>
-    <row r="243" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B243" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="E243"/>
-      <c r="F243"/>
-    </row>
-    <row r="244" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B244" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E244"/>
-      <c r="F244"/>
-    </row>
-    <row r="245" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B245" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E245"/>
-      <c r="F245"/>
-    </row>
-    <row r="246" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B246" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E246"/>
-      <c r="F246"/>
-    </row>
-    <row r="247" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B247" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E247"/>
-      <c r="F247"/>
-    </row>
-    <row r="248" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B248" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E248"/>
-      <c r="F248"/>
-    </row>
-    <row r="249" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B249" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="E249"/>
-      <c r="F249"/>
-    </row>
-    <row r="250" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B250" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="E250"/>
-      <c r="F250"/>
-    </row>
-    <row r="251" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B251" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="E251"/>
-      <c r="F251"/>
-    </row>
-    <row r="252" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B252" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="E252"/>
-      <c r="F252"/>
-    </row>
-    <row r="253" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B253" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E253"/>
-      <c r="F253"/>
-    </row>
-    <row r="254" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B254" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="E254"/>
-      <c r="F254"/>
-    </row>
-    <row r="255" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B255" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E255"/>
-      <c r="F255"/>
-    </row>
-    <row r="256" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B256" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C256" s="50" t="s">
+      <c r="C256" s="47" t="s">
         <v>1618</v>
       </c>
-      <c r="E256"/>
-      <c r="F256"/>
-    </row>
-    <row r="257" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B257" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="E257"/>
-      <c r="F257"/>
-    </row>
-    <row r="258" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B258" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="E258"/>
-      <c r="F258"/>
-    </row>
-    <row r="259" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B259" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E259"/>
-      <c r="F259"/>
-    </row>
-    <row r="260" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B260" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="E260"/>
-      <c r="F260"/>
-    </row>
-    <row r="261" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B261" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="E261"/>
-      <c r="F261"/>
-    </row>
-    <row r="262" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B262" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="E262"/>
-      <c r="F262"/>
-    </row>
-    <row r="263" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B263" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="E263"/>
-      <c r="F263"/>
-    </row>
-    <row r="264" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B264" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="E264"/>
-      <c r="F264"/>
-    </row>
-    <row r="265" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B265" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E265"/>
-      <c r="F265"/>
-    </row>
-    <row r="266" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B266" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="E266"/>
-      <c r="F266"/>
-    </row>
-    <row r="267" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B267" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="E267"/>
-      <c r="F267"/>
-    </row>
-    <row r="268" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B268" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="E268"/>
-      <c r="F268"/>
-    </row>
-    <row r="269" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B269" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="E269"/>
-      <c r="F269"/>
-    </row>
-    <row r="270" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B270" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E270"/>
-      <c r="F270"/>
-    </row>
-    <row r="271" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B271" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="E271"/>
-      <c r="F271"/>
-    </row>
-    <row r="272" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B272" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="E272"/>
-      <c r="F272"/>
-    </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B273" s="14" t="s">
         <v>1622</v>
       </c>
-      <c r="E273"/>
-      <c r="F273"/>
-    </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B274" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="E274"/>
-      <c r="F274"/>
-    </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B275" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="E275"/>
-      <c r="F275"/>
-    </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B276" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E276"/>
-      <c r="F276"/>
-    </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B277" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="E277"/>
-      <c r="F277"/>
-    </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B278" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="E278"/>
-      <c r="F278"/>
-    </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B279" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="E279"/>
-      <c r="F279"/>
-    </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B280" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="E280"/>
-      <c r="F280"/>
-    </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B281" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="E281"/>
-      <c r="F281"/>
-    </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B282" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E282"/>
-      <c r="F282"/>
-    </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B283" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E283"/>
-      <c r="F283"/>
-    </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B284" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E284"/>
-      <c r="F284"/>
-    </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B285" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E285"/>
-      <c r="F285"/>
-    </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B286" s="14" t="s">
         <v>1623</v>
       </c>
-      <c r="E286"/>
-      <c r="F286"/>
-    </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B287" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E287"/>
-      <c r="F287"/>
-    </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B288" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E288"/>
-      <c r="F288"/>
-    </row>
-    <row r="289" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B289" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E289"/>
-      <c r="F289"/>
-    </row>
-    <row r="290" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B290" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E290"/>
-      <c r="F290"/>
-    </row>
-    <row r="291" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B291" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="E291"/>
-      <c r="F291"/>
-    </row>
-    <row r="292" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B292" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E292"/>
-      <c r="F292"/>
-    </row>
-    <row r="293" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B293" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E293"/>
-      <c r="F293"/>
-    </row>
-    <row r="294" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B294" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E294"/>
-      <c r="F294"/>
-    </row>
-    <row r="295" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B295" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E295"/>
-      <c r="F295"/>
-    </row>
-    <row r="296" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B296" s="14" t="s">
         <v>1624</v>
       </c>
-      <c r="E296"/>
-      <c r="F296"/>
-    </row>
-    <row r="297" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B297" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C297" s="50" t="s">
+      <c r="C297" s="47" t="s">
         <v>1619</v>
       </c>
-      <c r="E297"/>
-      <c r="F297"/>
-    </row>
-    <row r="298" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B298" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="E298"/>
-      <c r="F298"/>
-    </row>
-    <row r="299" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B299" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="E299"/>
-      <c r="F299"/>
-    </row>
-    <row r="300" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B300" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="E300"/>
-      <c r="F300"/>
-    </row>
-    <row r="301" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B301" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E301"/>
-      <c r="F301"/>
-    </row>
-    <row r="302" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B302" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="E302"/>
-      <c r="F302"/>
-    </row>
-    <row r="303" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B303" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E303"/>
-      <c r="F303"/>
-    </row>
-    <row r="304" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B304" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E304"/>
-      <c r="F304"/>
-    </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B305" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E305"/>
-      <c r="F305"/>
-    </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B306" s="41" t="s">
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B306" t="s">
         <v>22</v>
       </c>
-      <c r="E306"/>
-      <c r="F306"/>
-    </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B307" s="41" t="s">
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B307" t="s">
         <v>265</v>
       </c>
-      <c r="E307"/>
-      <c r="F307"/>
-    </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B308" s="41" t="s">
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B308" t="s">
         <v>376</v>
       </c>
-      <c r="E308"/>
-      <c r="F308"/>
-    </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B309" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E309"/>
-      <c r="F309"/>
-    </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B310" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E310"/>
-      <c r="F310"/>
-    </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B311" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E311"/>
-      <c r="F311"/>
-    </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B312" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="C312" s="41" t="s">
+      <c r="C312" t="s">
         <v>1621</v>
       </c>
-      <c r="E312"/>
-      <c r="F312"/>
-    </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B313" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="E313"/>
-      <c r="F313"/>
-    </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B314" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="E314"/>
-      <c r="F314"/>
-    </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B315" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="E315"/>
-      <c r="F315"/>
-    </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B316" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="E316"/>
-      <c r="F316"/>
-    </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B317" s="14" t="s">
         <v>1626</v>
       </c>
-      <c r="E317"/>
-      <c r="F317"/>
-    </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B318" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="E318"/>
-      <c r="F318"/>
-    </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B319" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="E319"/>
-      <c r="F319"/>
-    </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B320" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="E320"/>
-      <c r="F320"/>
-    </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B321" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="E321"/>
-      <c r="F321"/>
-    </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B322" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="E322"/>
-      <c r="F322"/>
-    </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B323" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="E323"/>
-      <c r="F323"/>
-    </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B324" s="14" t="s">
         <v>1625</v>
       </c>
-      <c r="E324"/>
-      <c r="F324"/>
-    </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B325" s="14" t="s">
         <v>1627</v>
       </c>
-      <c r="E325"/>
-      <c r="F325"/>
-    </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B326" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E326"/>
-      <c r="F326"/>
-    </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B327" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E327"/>
-      <c r="F327"/>
-    </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B328" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E328"/>
-      <c r="F328"/>
-    </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B329" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E329"/>
-      <c r="F329"/>
-    </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B330" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="E330"/>
-      <c r="F330"/>
-    </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B331" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E331"/>
-      <c r="F331"/>
-    </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B332" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="E332"/>
-      <c r="F332"/>
-    </row>
-    <row r="333" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B333" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E333"/>
-      <c r="F333"/>
-    </row>
-    <row r="334" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B334" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E334"/>
-      <c r="F334"/>
-    </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B335" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E335"/>
-      <c r="F335"/>
-    </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B336" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E336"/>
-      <c r="F336"/>
-    </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B337" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="E337"/>
-      <c r="F337"/>
-    </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B338" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E338"/>
-      <c r="F338"/>
-    </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B339" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E339"/>
-      <c r="F339"/>
-    </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B340" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E340"/>
-      <c r="F340"/>
-    </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B341" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E341"/>
-      <c r="F341"/>
-    </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B342" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E342"/>
-      <c r="F342"/>
-    </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B343" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E343"/>
-      <c r="F343"/>
-    </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B344" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E344"/>
-      <c r="F344"/>
-    </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B345" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E345"/>
-      <c r="F345"/>
-    </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B346" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="E346"/>
-      <c r="F346"/>
-    </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B347" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="E347"/>
-      <c r="F347"/>
-    </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B348" s="16" t="s">
         <v>1630</v>
       </c>
-      <c r="E348"/>
-      <c r="F348"/>
-    </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B349" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="E349"/>
-      <c r="F349"/>
-    </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B350" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="E350"/>
-      <c r="F350"/>
-    </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B351" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E351"/>
-      <c r="F351"/>
-    </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B352" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E352"/>
-      <c r="F352"/>
-    </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B353" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E353"/>
-      <c r="F353"/>
-    </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B354" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E354"/>
-      <c r="F354"/>
-    </row>
-    <row r="355" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B355" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E355"/>
-      <c r="F355"/>
-    </row>
-    <row r="356" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B356" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E356"/>
-      <c r="F356"/>
-    </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B357" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E357"/>
-      <c r="F357"/>
-    </row>
-    <row r="358" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B358" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E358"/>
-      <c r="F358"/>
-    </row>
-    <row r="359" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B359" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="E359"/>
-      <c r="F359"/>
-    </row>
-    <row r="360" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B360" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E360"/>
-      <c r="F360"/>
-    </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B361" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="E361"/>
-      <c r="F361"/>
-    </row>
-    <row r="362" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B362" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="E362"/>
-      <c r="F362"/>
-    </row>
-    <row r="363" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B363" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="E363"/>
-      <c r="F363"/>
-    </row>
-    <row r="364" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B364" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="E364"/>
-      <c r="F364"/>
-    </row>
-    <row r="365" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B365" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E365"/>
-      <c r="F365"/>
-    </row>
-    <row r="366" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B366" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E366"/>
-      <c r="F366"/>
-    </row>
-    <row r="367" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B367" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E367"/>
-      <c r="F367"/>
-    </row>
-    <row r="368" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B368" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="E368"/>
-      <c r="F368"/>
-    </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B369" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="E369"/>
-      <c r="F369"/>
-    </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B370" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E370"/>
-      <c r="F370"/>
-    </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B371" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="E371"/>
-      <c r="F371"/>
-    </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B372" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E372"/>
-      <c r="F372"/>
-    </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B373" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="E373"/>
-      <c r="F373"/>
-    </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B374" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E374"/>
-      <c r="F374"/>
-    </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B375" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="E375"/>
-      <c r="F375"/>
-    </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B376" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="E376"/>
-      <c r="F376"/>
-    </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B377" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E377"/>
-      <c r="F377"/>
-    </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B378" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E378"/>
-      <c r="F378"/>
-    </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B379" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="E379"/>
-      <c r="F379"/>
-    </row>
-    <row r="380" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B380" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="E380"/>
-      <c r="F380"/>
-    </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B381" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="E381"/>
-      <c r="F381"/>
-    </row>
-    <row r="382" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B382" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="E382"/>
-      <c r="F382"/>
-    </row>
-    <row r="383" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B383" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E383"/>
-      <c r="F383"/>
-    </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B384" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="E384"/>
-      <c r="F384"/>
-    </row>
-    <row r="385" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B385" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="E385"/>
-      <c r="F385"/>
-    </row>
-    <row r="386" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B386" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="E386"/>
-      <c r="F386"/>
-    </row>
-    <row r="387" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B387" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="E387"/>
-      <c r="F387"/>
-    </row>
-    <row r="388" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B388" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="E388"/>
-      <c r="F388"/>
-    </row>
-    <row r="389" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B389" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="E389"/>
-      <c r="F389"/>
-    </row>
-    <row r="390" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B390" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="E390"/>
-      <c r="F390"/>
-    </row>
-    <row r="391" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B391" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E391"/>
-      <c r="F391"/>
-    </row>
-    <row r="392" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B392" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="E392"/>
-      <c r="F392"/>
-    </row>
-    <row r="393" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B393" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="E393"/>
-      <c r="F393"/>
-    </row>
-    <row r="394" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B394" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="E394"/>
-      <c r="F394"/>
-    </row>
-    <row r="395" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B395" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="E395"/>
-      <c r="F395"/>
-    </row>
-    <row r="396" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B396" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E396"/>
-      <c r="F396"/>
-    </row>
-    <row r="397" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B397" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="E397"/>
-      <c r="F397"/>
-    </row>
-    <row r="398" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B398" s="41" t="s">
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B398" t="s">
         <v>382</v>
       </c>
-      <c r="E398"/>
-      <c r="F398"/>
-    </row>
-    <row r="399" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B399" s="41" t="s">
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B399" t="s">
         <v>384</v>
       </c>
-      <c r="E399"/>
-      <c r="F399"/>
-    </row>
-    <row r="400" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B400" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="E400"/>
-      <c r="F400"/>
-    </row>
-    <row r="401" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B401" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="E401"/>
-      <c r="F401"/>
-    </row>
-    <row r="402" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B402" s="41" t="s">
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B402" t="s">
         <v>424</v>
       </c>
-      <c r="E402"/>
-      <c r="F402"/>
-    </row>
-    <row r="403" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B403" s="41" t="s">
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B403" t="s">
         <v>425</v>
       </c>
-      <c r="E403"/>
-      <c r="F403"/>
-    </row>
-    <row r="404" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B404" s="47" t="s">
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B404" s="46" t="s">
         <v>454</v>
       </c>
-      <c r="E404"/>
-      <c r="F404"/>
-    </row>
-    <row r="405" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B405" s="47" t="s">
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B405" s="46" t="s">
         <v>455</v>
       </c>
-      <c r="E405"/>
-      <c r="F405"/>
-    </row>
-    <row r="406" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B406" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="E406"/>
-      <c r="F406"/>
-    </row>
-    <row r="407" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B407" s="14" t="s">
         <v>834</v>
       </c>
-      <c r="E407"/>
-      <c r="F407"/>
-    </row>
-    <row r="408" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B408" s="14" t="s">
         <v>835</v>
       </c>
-      <c r="E408"/>
-      <c r="F408"/>
-    </row>
-    <row r="409" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B409" s="45" t="s">
+    </row>
+    <row r="409" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B409" s="44" t="s">
         <v>836</v>
       </c>
-      <c r="E409"/>
-      <c r="F409"/>
-    </row>
-    <row r="410" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B410" s="14" t="s">
         <v>837</v>
       </c>
-      <c r="E410"/>
-      <c r="F410"/>
-    </row>
-    <row r="411" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B411" s="14" t="s">
         <v>838</v>
       </c>
-      <c r="E411"/>
-      <c r="F411"/>
-    </row>
-    <row r="412" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B412" s="14" t="s">
         <v>839</v>
       </c>
-      <c r="E412"/>
-      <c r="F412"/>
-    </row>
-    <row r="413" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B413" s="14" t="s">
         <v>840</v>
       </c>
-      <c r="E413"/>
-      <c r="F413"/>
-    </row>
-    <row r="414" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B414" s="14" t="s">
         <v>841</v>
       </c>
-      <c r="E414"/>
-      <c r="F414"/>
-    </row>
-    <row r="415" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B415" s="14" t="s">
         <v>842</v>
       </c>
-      <c r="E415"/>
-      <c r="F415"/>
-    </row>
-    <row r="416" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B416" s="14" t="s">
         <v>843</v>
       </c>
-      <c r="E416"/>
-      <c r="F416"/>
-    </row>
-    <row r="417" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B417" s="14" t="s">
         <v>844</v>
       </c>
-      <c r="E417"/>
-      <c r="F417"/>
-    </row>
-    <row r="418" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B418" s="14" t="s">
         <v>845</v>
       </c>
-      <c r="E418"/>
-      <c r="F418"/>
-    </row>
-    <row r="419" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B419" s="14" t="s">
         <v>846</v>
       </c>
-      <c r="E419"/>
-      <c r="F419"/>
-    </row>
-    <row r="420" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B420" s="14" t="s">
         <v>847</v>
       </c>
-      <c r="E420"/>
-      <c r="F420"/>
-    </row>
-    <row r="421" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B421" s="45" t="s">
+    </row>
+    <row r="421" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B421" s="44" t="s">
         <v>879</v>
       </c>
-      <c r="E421"/>
-      <c r="F421"/>
-    </row>
-    <row r="422" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B422" s="45" t="s">
+    </row>
+    <row r="422" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B422" s="44" t="s">
         <v>880</v>
       </c>
-      <c r="E422"/>
-      <c r="F422"/>
-    </row>
-    <row r="423" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B423" s="45" t="s">
+    </row>
+    <row r="423" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B423" s="44" t="s">
         <v>881</v>
       </c>
-      <c r="E423"/>
-      <c r="F423"/>
-    </row>
-    <row r="424" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B424" s="45" t="s">
+    </row>
+    <row r="424" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B424" s="44" t="s">
         <v>882</v>
       </c>
-      <c r="E424"/>
-      <c r="F424"/>
-    </row>
-    <row r="425" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B425" s="45" t="s">
+    </row>
+    <row r="425" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B425" s="44" t="s">
         <v>883</v>
       </c>
-      <c r="E425"/>
-      <c r="F425"/>
-    </row>
-    <row r="426" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B426" s="45" t="s">
+    </row>
+    <row r="426" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B426" s="44" t="s">
         <v>884</v>
       </c>
-      <c r="E426"/>
-      <c r="F426"/>
-    </row>
-    <row r="427" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B427" s="45" t="s">
+    </row>
+    <row r="427" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B427" s="44" t="s">
         <v>885</v>
       </c>
-      <c r="E427"/>
-      <c r="F427"/>
-    </row>
-    <row r="428" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B428" s="45" t="s">
+    </row>
+    <row r="428" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B428" s="44" t="s">
         <v>886</v>
       </c>
-      <c r="E428"/>
-      <c r="F428"/>
-    </row>
-    <row r="429" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B429" s="45" t="s">
+    </row>
+    <row r="429" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B429" s="44" t="s">
         <v>887</v>
       </c>
-      <c r="E429"/>
-      <c r="F429"/>
-    </row>
-    <row r="430" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B430" s="45" t="s">
+    </row>
+    <row r="430" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B430" s="44" t="s">
         <v>888</v>
       </c>
-      <c r="E430"/>
-      <c r="F430"/>
-    </row>
-    <row r="431" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B431" s="45" t="s">
+    </row>
+    <row r="431" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B431" s="44" t="s">
         <v>889</v>
       </c>
-      <c r="E431"/>
-      <c r="F431"/>
-    </row>
-    <row r="432" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B432" s="45" t="s">
+    </row>
+    <row r="432" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B432" s="44" t="s">
         <v>890</v>
       </c>
-      <c r="E432"/>
-      <c r="F432"/>
-    </row>
-    <row r="433" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B433" s="45" t="s">
+    </row>
+    <row r="433" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B433" s="44" t="s">
         <v>891</v>
       </c>
-      <c r="E433"/>
-      <c r="F433"/>
-    </row>
-    <row r="434" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B434" s="45" t="s">
+    </row>
+    <row r="434" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B434" s="44" t="s">
         <v>892</v>
       </c>
-      <c r="E434"/>
-      <c r="F434"/>
-    </row>
-    <row r="435" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B435" s="45" t="s">
+    </row>
+    <row r="435" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B435" s="44" t="s">
         <v>893</v>
       </c>
-      <c r="E435"/>
-      <c r="F435"/>
-    </row>
-    <row r="436" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B436" s="45" t="s">
+    </row>
+    <row r="436" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B436" s="44" t="s">
         <v>894</v>
       </c>
-      <c r="E436"/>
-      <c r="F436"/>
-    </row>
-    <row r="437" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B437" s="45" t="s">
+    </row>
+    <row r="437" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B437" s="44" t="s">
         <v>895</v>
       </c>
-      <c r="C437" s="45" t="s">
+      <c r="C437" s="44" t="s">
         <v>848</v>
       </c>
-      <c r="E437"/>
-      <c r="F437"/>
-    </row>
-    <row r="438" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B438" s="45" t="s">
+    </row>
+    <row r="438" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B438" s="44" t="s">
         <v>896</v>
       </c>
-      <c r="E438"/>
-      <c r="F438"/>
-    </row>
-    <row r="439" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B439" s="45" t="s">
+    </row>
+    <row r="439" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B439" s="44" t="s">
         <v>897</v>
       </c>
-      <c r="E439"/>
-      <c r="F439"/>
-    </row>
-    <row r="440" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B440" s="45" t="s">
+    </row>
+    <row r="440" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B440" s="44" t="s">
         <v>898</v>
       </c>
-      <c r="E440"/>
-      <c r="F440"/>
-    </row>
-    <row r="441" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B441" s="45" t="s">
+    </row>
+    <row r="441" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B441" s="44" t="s">
         <v>899</v>
       </c>
-      <c r="E441"/>
-      <c r="F441"/>
-    </row>
-    <row r="442" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B442" s="45" t="s">
+    </row>
+    <row r="442" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B442" s="44" t="s">
         <v>900</v>
       </c>
-      <c r="E442"/>
-      <c r="F442"/>
-    </row>
-    <row r="443" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B443" s="45" t="s">
+    </row>
+    <row r="443" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B443" s="44" t="s">
         <v>901</v>
       </c>
-      <c r="E443"/>
-      <c r="F443"/>
-    </row>
-    <row r="444" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B444" s="45" t="s">
+    </row>
+    <row r="444" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B444" s="44" t="s">
         <v>902</v>
       </c>
-      <c r="E444"/>
-      <c r="F444"/>
-    </row>
-    <row r="445" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B445" s="45" t="s">
+    </row>
+    <row r="445" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B445" s="44" t="s">
         <v>903</v>
       </c>
-      <c r="E445"/>
-      <c r="F445"/>
-    </row>
-    <row r="446" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B446" s="45" t="s">
+    </row>
+    <row r="446" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B446" s="44" t="s">
         <v>904</v>
       </c>
-      <c r="E446"/>
-      <c r="F446"/>
-    </row>
-    <row r="447" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B447" s="45" t="s">
+    </row>
+    <row r="447" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B447" s="44" t="s">
         <v>905</v>
       </c>
-      <c r="E447"/>
-      <c r="F447"/>
-    </row>
-    <row r="448" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B448" s="45" t="s">
+    </row>
+    <row r="448" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="B448" s="44" t="s">
         <v>906</v>
       </c>
-      <c r="E448"/>
-      <c r="F448"/>
-    </row>
-    <row r="449" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B449" s="45" t="s">
+    </row>
+    <row r="449" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B449" s="44" t="s">
         <v>907</v>
       </c>
-      <c r="E449"/>
-      <c r="F449"/>
-    </row>
-    <row r="450" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B450" s="45" t="s">
+    </row>
+    <row r="450" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B450" s="44" t="s">
         <v>908</v>
       </c>
-      <c r="E450"/>
-      <c r="F450"/>
-    </row>
-    <row r="451" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B451" s="45" t="s">
+    </row>
+    <row r="451" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B451" s="44" t="s">
         <v>909</v>
       </c>
-      <c r="E451"/>
-      <c r="F451"/>
-    </row>
-    <row r="452" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B452" s="45" t="s">
+    </row>
+    <row r="452" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B452" s="44" t="s">
         <v>910</v>
       </c>
-      <c r="E452"/>
-      <c r="F452"/>
-    </row>
-    <row r="453" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B453" s="45" t="s">
+    </row>
+    <row r="453" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B453" s="44" t="s">
         <v>911</v>
       </c>
-      <c r="E453"/>
-      <c r="F453"/>
-    </row>
-    <row r="454" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B454" s="45" t="s">
+    </row>
+    <row r="454" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B454" s="44" t="s">
         <v>912</v>
       </c>
-      <c r="E454"/>
-      <c r="F454"/>
-    </row>
-    <row r="455" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B455" s="45" t="s">
+    </row>
+    <row r="455" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B455" s="44" t="s">
         <v>913</v>
       </c>
-      <c r="E455"/>
-      <c r="F455"/>
-    </row>
-    <row r="456" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B456" s="45" t="s">
+    </row>
+    <row r="456" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B456" s="44" t="s">
         <v>914</v>
       </c>
-      <c r="E456"/>
-      <c r="F456"/>
-    </row>
-    <row r="457" spans="2:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="B457" s="45" t="s">
+    </row>
+    <row r="457" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B457" s="44" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C475" s="41" t="s">
+      <c r="C475" t="s">
         <v>848</v>
       </c>
     </row>
